--- a/合并后的人员信息.xlsx
+++ b/合并后的人员信息.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,11 +437,6 @@
           <t>是否已婚</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>_source</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -462,11 +457,6 @@
           <t>是</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>两个表都有</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,11 +475,6 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>否</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>两个表都有</t>
         </is>
       </c>
     </row>
